--- a/artfynd/A 62393-2023 artfynd.xlsx
+++ b/artfynd/A 62393-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62393-2023 artfynd.xlsx
+++ b/artfynd/A 62393-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63350123</v>
+        <v>78640820</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klöverberget 1.2, Vb</t>
+          <t>Klöverberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763798.7459460206</v>
+        <v>763754</v>
       </c>
       <c r="R2" t="n">
-        <v>7231419.774861161</v>
+        <v>7231531</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,51 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>vanlig sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Åsa Stenman, Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63350064</v>
+        <v>78640821</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,43 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klöverberget 1.2, Vb</t>
+          <t>Klöverberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763766.283344665</v>
+        <v>763755</v>
       </c>
       <c r="R3" t="n">
-        <v>7231531.658005942</v>
+        <v>7231511</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,49 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Åsa Stenman, Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63350082</v>
+        <v>63350064</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763775.7612790004</v>
+        <v>763766</v>
       </c>
       <c r="R4" t="n">
-        <v>7231572.73995384</v>
+        <v>7231532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,19 +943,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,59 +972,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63350102</v>
+        <v>78640866</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klöverberget 1.2, Vb</t>
+          <t>Klöverberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>763912.5450849514</v>
+        <v>763911</v>
       </c>
       <c r="R5" t="n">
-        <v>7231598.507112151</v>
+        <v>7231538</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,22 +1037,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,12 +1057,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Henrik Sporrong, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1170,12 +1072,7 @@
         <v>63350049</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763769.427304894</v>
+        <v>763769</v>
       </c>
       <c r="R6" t="n">
-        <v>7231624.692095676</v>
+        <v>7231625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,19 +1139,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,15 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63350092</v>
+        <v>63350057</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>763773.8696203025</v>
+        <v>763755</v>
       </c>
       <c r="R7" t="n">
-        <v>7231584.429973111</v>
+        <v>7231601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,19 +1242,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,15 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63350057</v>
+        <v>63350082</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>763754.5505434535</v>
+        <v>763776</v>
       </c>
       <c r="R8" t="n">
-        <v>7231601.340690395</v>
+        <v>7231573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,19 +1345,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,37 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63350061</v>
+        <v>63350092</v>
       </c>
       <c r="B9" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1563,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763754.5505434535</v>
+        <v>763774</v>
       </c>
       <c r="R9" t="n">
-        <v>7231601.340690395</v>
+        <v>7231584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,19 +1448,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,12 +1480,7 @@
         <v>63350100</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>763788.4006832956</v>
+        <v>763788</v>
       </c>
       <c r="R10" t="n">
-        <v>7231606.903698713</v>
+        <v>7231607</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1714,19 +1551,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,15 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>78640820</v>
+        <v>63350102</v>
       </c>
       <c r="B11" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,37 +1591,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klöverberget, Vb</t>
+          <t>Klöverberget 1.2, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>763754.0457740342</v>
+        <v>763913</v>
       </c>
       <c r="R11" t="n">
-        <v>7231530.989161881</v>
+        <v>7231599</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,22 +1651,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-09-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-09-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,27 +1671,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Åsa Stenman, Henrik Sporrong</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>78640821</v>
+        <v>63350106</v>
       </c>
       <c r="B12" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,37 +1694,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Klöverberget, Vb</t>
+          <t>Klöverberget 1.2, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>763754.9672284955</v>
+        <v>763919</v>
       </c>
       <c r="R12" t="n">
-        <v>7231511.165066435</v>
+        <v>7231533</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1935,22 +1754,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-09-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-09-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,15 +1774,673 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>63350123</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Klöverberget 1.2, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>763799</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7231420</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>vanlig sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>63350155</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Klöverberget 1.2, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>763950</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7231533</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>63350163</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Klöverberget 1.2, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>763953</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7231545</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>vanlig sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>urgammal sälg</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea # urgammal sälg</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>78640867</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klöverberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>763914</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7231540</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Åsa Stenman</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Åsa Stenman, Henrik Sporrong</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henrik Sporrong, Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>63350061</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klöverberget 1.2, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>763755</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7231601</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>63350109</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klöverberget 1.2, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>763919</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7231533</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2015-06-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62393-2023 artfynd.xlsx
+++ b/artfynd/A 62393-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78640820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78640821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350064</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1066,6 +1086,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78640866</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350049</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350092</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350100</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1680,6 +1730,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350102</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350106</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350123</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350155</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350163</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2235,6 +2310,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78640867</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2338,6 +2418,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350061</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,8 +2526,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63350109</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>